--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -5455,10 +5455,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121108157</v>
+        <v>121108905</v>
       </c>
       <c r="B42" t="n">
-        <v>94844</v>
+        <v>8432</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5471,31 +5471,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5503,13 +5500,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>693874</v>
+        <v>693732</v>
       </c>
       <c r="R42" t="n">
-        <v>6552257</v>
+        <v>6552059</v>
       </c>
       <c r="S42" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5538,7 +5535,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5548,7 +5545,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5575,10 +5572,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121108905</v>
+        <v>121108431</v>
       </c>
       <c r="B43" t="n">
-        <v>8432</v>
+        <v>100347</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5591,28 +5588,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5620,13 +5616,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693732</v>
+        <v>693829</v>
       </c>
       <c r="R43" t="n">
-        <v>6552059</v>
+        <v>6552190</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5655,7 +5651,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5665,7 +5661,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5692,10 +5688,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121108431</v>
+        <v>121108157</v>
       </c>
       <c r="B44" t="n">
-        <v>100337</v>
+        <v>94854</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5708,24 +5704,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -5736,13 +5736,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>693829</v>
+        <v>693874</v>
       </c>
       <c r="R44" t="n">
-        <v>6552190</v>
+        <v>6552257</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5910,10 +5910,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121125725</v>
+        <v>121125740</v>
       </c>
       <c r="B46" t="n">
-        <v>94594</v>
+        <v>8421</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5926,21 +5926,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693735</v>
+        <v>693742</v>
       </c>
       <c r="R46" t="n">
-        <v>6552057</v>
+        <v>6552063</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5994,7 +5994,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6013,10 +6012,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121125740</v>
+        <v>121125725</v>
       </c>
       <c r="B47" t="n">
-        <v>8421</v>
+        <v>94604</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6029,21 +6028,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6053,10 +6052,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>693742</v>
+        <v>693735</v>
       </c>
       <c r="R47" t="n">
-        <v>6552063</v>
+        <v>6552057</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6097,6 +6096,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>121228311</v>
       </c>
       <c r="B48" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>121125734</v>
       </c>
       <c r="B49" t="n">
-        <v>94690</v>
+        <v>94700</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>121342637</v>
       </c>
       <c r="B52" t="n">
-        <v>94594</v>
+        <v>94604</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -5455,10 +5455,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121108905</v>
+        <v>121108431</v>
       </c>
       <c r="B42" t="n">
-        <v>8432</v>
+        <v>100347</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5471,28 +5471,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5500,13 +5499,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>693732</v>
+        <v>693829</v>
       </c>
       <c r="R42" t="n">
-        <v>6552059</v>
+        <v>6552190</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5535,7 +5534,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5545,7 +5544,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5572,10 +5571,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121108431</v>
+        <v>121108157</v>
       </c>
       <c r="B43" t="n">
-        <v>100347</v>
+        <v>94854</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5588,24 +5587,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -5616,13 +5619,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693829</v>
+        <v>693874</v>
       </c>
       <c r="R43" t="n">
-        <v>6552190</v>
+        <v>6552257</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5651,7 +5654,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5661,7 +5664,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5688,10 +5691,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121108157</v>
+        <v>121108905</v>
       </c>
       <c r="B44" t="n">
-        <v>94854</v>
+        <v>8432</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5704,31 +5707,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2180</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5736,13 +5736,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>693874</v>
+        <v>693732</v>
       </c>
       <c r="R44" t="n">
-        <v>6552257</v>
+        <v>6552059</v>
       </c>
       <c r="S44" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5808,10 +5808,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121125724</v>
+        <v>121125740</v>
       </c>
       <c r="B45" t="n">
-        <v>5189</v>
+        <v>8421</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5824,21 +5824,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>693779</v>
+        <v>693742</v>
       </c>
       <c r="R45" t="n">
-        <v>6552034</v>
+        <v>6552063</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5910,10 +5910,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121125740</v>
+        <v>121125725</v>
       </c>
       <c r="B46" t="n">
-        <v>8421</v>
+        <v>94604</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5926,21 +5926,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693742</v>
+        <v>693735</v>
       </c>
       <c r="R46" t="n">
-        <v>6552063</v>
+        <v>6552057</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5994,6 +5994,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6012,10 +6013,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121125725</v>
+        <v>121125724</v>
       </c>
       <c r="B47" t="n">
-        <v>94604</v>
+        <v>5189</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6028,21 +6029,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6052,10 +6053,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>693735</v>
+        <v>693779</v>
       </c>
       <c r="R47" t="n">
-        <v>6552057</v>
+        <v>6552034</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6096,7 +6097,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -5458,7 +5458,7 @@
         <v>121108431</v>
       </c>
       <c r="B42" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>121108157</v>
       </c>
       <c r="B43" t="n">
-        <v>94854</v>
+        <v>94866</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5910,10 +5910,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121125725</v>
+        <v>121125724</v>
       </c>
       <c r="B46" t="n">
-        <v>94604</v>
+        <v>5189</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5926,21 +5926,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693735</v>
+        <v>693779</v>
       </c>
       <c r="R46" t="n">
-        <v>6552057</v>
+        <v>6552034</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5994,7 +5994,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6013,10 +6012,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121125724</v>
+        <v>121125725</v>
       </c>
       <c r="B47" t="n">
-        <v>5189</v>
+        <v>94616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6029,21 +6028,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6053,10 +6052,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>693779</v>
+        <v>693735</v>
       </c>
       <c r="R47" t="n">
-        <v>6552034</v>
+        <v>6552057</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6097,6 +6096,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>121228311</v>
       </c>
       <c r="B48" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6221,10 +6221,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121125734</v>
+        <v>121125733</v>
       </c>
       <c r="B49" t="n">
-        <v>94700</v>
+        <v>5168</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6233,25 +6233,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>210</v>
+        <v>102204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693862</v>
+        <v>694003</v>
       </c>
       <c r="R49" t="n">
-        <v>6552120</v>
+        <v>6552176</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6323,10 +6323,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121125733</v>
+        <v>121125734</v>
       </c>
       <c r="B50" t="n">
-        <v>5168</v>
+        <v>94712</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6335,25 +6335,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102204</v>
+        <v>210</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>694003</v>
+        <v>693862</v>
       </c>
       <c r="R50" t="n">
-        <v>6552176</v>
+        <v>6552120</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6550,7 +6550,7 @@
         <v>121342637</v>
       </c>
       <c r="B52" t="n">
-        <v>94604</v>
+        <v>94616</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -5458,7 +5458,7 @@
         <v>121108431</v>
       </c>
       <c r="B42" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>121108157</v>
       </c>
       <c r="B43" t="n">
-        <v>94866</v>
+        <v>94867</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121125740</v>
+        <v>121125724</v>
       </c>
       <c r="B45" t="n">
-        <v>8421</v>
+        <v>5189</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5824,21 +5824,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>693742</v>
+        <v>693779</v>
       </c>
       <c r="R45" t="n">
-        <v>6552063</v>
+        <v>6552034</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5910,10 +5910,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121125724</v>
+        <v>121125725</v>
       </c>
       <c r="B46" t="n">
-        <v>5189</v>
+        <v>94617</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5926,21 +5926,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693779</v>
+        <v>693735</v>
       </c>
       <c r="R46" t="n">
-        <v>6552034</v>
+        <v>6552057</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5994,6 +5994,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6012,10 +6013,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121125725</v>
+        <v>121125740</v>
       </c>
       <c r="B47" t="n">
-        <v>94616</v>
+        <v>8421</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6028,21 +6029,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6052,10 +6053,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>693735</v>
+        <v>693742</v>
       </c>
       <c r="R47" t="n">
-        <v>6552057</v>
+        <v>6552063</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6096,7 +6097,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>121125734</v>
       </c>
       <c r="B50" t="n">
-        <v>94712</v>
+        <v>94713</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>121342637</v>
       </c>
       <c r="B52" t="n">
-        <v>94616</v>
+        <v>94617</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -5455,10 +5455,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121108431</v>
+        <v>121108157</v>
       </c>
       <c r="B42" t="n">
-        <v>100361</v>
+        <v>94870</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5471,24 +5471,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -5499,13 +5503,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>693829</v>
+        <v>693874</v>
       </c>
       <c r="R42" t="n">
-        <v>6552190</v>
+        <v>6552257</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5534,7 +5538,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5544,7 +5548,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5571,10 +5575,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121108157</v>
+        <v>121108431</v>
       </c>
       <c r="B43" t="n">
-        <v>94867</v>
+        <v>100364</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5587,28 +5591,24 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -5619,13 +5619,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693874</v>
+        <v>693829</v>
       </c>
       <c r="R43" t="n">
-        <v>6552257</v>
+        <v>6552190</v>
       </c>
       <c r="S43" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5694,7 +5694,7 @@
         <v>121108905</v>
       </c>
       <c r="B44" t="n">
-        <v>8432</v>
+        <v>8435</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>121125724</v>
       </c>
       <c r="B45" t="n">
-        <v>5189</v>
+        <v>5192</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>121125725</v>
       </c>
       <c r="B46" t="n">
-        <v>94617</v>
+        <v>94620</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>121125740</v>
       </c>
       <c r="B47" t="n">
-        <v>8421</v>
+        <v>8424</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>121228311</v>
       </c>
       <c r="B48" t="n">
-        <v>79222</v>
+        <v>79225</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6221,10 +6221,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121125733</v>
+        <v>121125734</v>
       </c>
       <c r="B49" t="n">
-        <v>5168</v>
+        <v>94716</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6233,25 +6233,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102204</v>
+        <v>210</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>694003</v>
+        <v>693862</v>
       </c>
       <c r="R49" t="n">
-        <v>6552176</v>
+        <v>6552120</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6323,10 +6323,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121125734</v>
+        <v>121125733</v>
       </c>
       <c r="B50" t="n">
-        <v>94713</v>
+        <v>5171</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6335,25 +6335,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>210</v>
+        <v>102204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>693862</v>
+        <v>694003</v>
       </c>
       <c r="R50" t="n">
-        <v>6552120</v>
+        <v>6552176</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6428,7 +6428,7 @@
         <v>121108561</v>
       </c>
       <c r="B51" t="n">
-        <v>8421</v>
+        <v>8424</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>121342637</v>
       </c>
       <c r="B52" t="n">
-        <v>94617</v>
+        <v>94620</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -5455,10 +5455,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121108157</v>
+        <v>121108431</v>
       </c>
       <c r="B42" t="n">
-        <v>94870</v>
+        <v>100364</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5471,28 +5471,24 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -5503,13 +5499,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>693874</v>
+        <v>693829</v>
       </c>
       <c r="R42" t="n">
-        <v>6552257</v>
+        <v>6552190</v>
       </c>
       <c r="S42" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5538,7 +5534,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5548,7 +5544,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5575,10 +5571,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121108431</v>
+        <v>121108157</v>
       </c>
       <c r="B43" t="n">
-        <v>100364</v>
+        <v>94870</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5591,24 +5587,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -5619,13 +5619,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693829</v>
+        <v>693874</v>
       </c>
       <c r="R43" t="n">
-        <v>6552190</v>
+        <v>6552257</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5808,10 +5808,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121125724</v>
+        <v>121125725</v>
       </c>
       <c r="B45" t="n">
-        <v>5192</v>
+        <v>94620</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5824,21 +5824,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>693779</v>
+        <v>693735</v>
       </c>
       <c r="R45" t="n">
-        <v>6552034</v>
+        <v>6552057</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5892,6 +5892,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5910,10 +5911,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121125725</v>
+        <v>121125724</v>
       </c>
       <c r="B46" t="n">
-        <v>94620</v>
+        <v>5192</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5926,21 +5927,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5950,10 +5951,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693735</v>
+        <v>693779</v>
       </c>
       <c r="R46" t="n">
-        <v>6552057</v>
+        <v>6552034</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5994,7 +5995,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6221,10 +6221,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121125734</v>
+        <v>121125733</v>
       </c>
       <c r="B49" t="n">
-        <v>94716</v>
+        <v>5171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6233,25 +6233,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>210</v>
+        <v>102204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693862</v>
+        <v>694003</v>
       </c>
       <c r="R49" t="n">
-        <v>6552120</v>
+        <v>6552176</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6323,10 +6323,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121125733</v>
+        <v>121125734</v>
       </c>
       <c r="B50" t="n">
-        <v>5171</v>
+        <v>94716</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6335,25 +6335,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102204</v>
+        <v>210</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>694003</v>
+        <v>693862</v>
       </c>
       <c r="R50" t="n">
-        <v>6552176</v>
+        <v>6552120</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -6118,7 +6118,7 @@
         <v>121228311</v>
       </c>
       <c r="B48" t="n">
-        <v>79225</v>
+        <v>79226</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6221,10 +6221,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121125733</v>
+        <v>121125734</v>
       </c>
       <c r="B49" t="n">
-        <v>5171</v>
+        <v>94722</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6233,25 +6233,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102204</v>
+        <v>210</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>694003</v>
+        <v>693862</v>
       </c>
       <c r="R49" t="n">
-        <v>6552176</v>
+        <v>6552120</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6323,10 +6323,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121125734</v>
+        <v>121125733</v>
       </c>
       <c r="B50" t="n">
-        <v>94716</v>
+        <v>5171</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6335,25 +6335,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>210</v>
+        <v>102204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>693862</v>
+        <v>694003</v>
       </c>
       <c r="R50" t="n">
-        <v>6552120</v>
+        <v>6552176</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6550,7 +6550,7 @@
         <v>121342637</v>
       </c>
       <c r="B52" t="n">
-        <v>94620</v>
+        <v>94626</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -6118,7 +6118,7 @@
         <v>121228311</v>
       </c>
       <c r="B48" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>121125734</v>
       </c>
       <c r="B49" t="n">
-        <v>94722</v>
+        <v>94723</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>121342637</v>
       </c>
       <c r="B52" t="n">
-        <v>94626</v>
+        <v>94627</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -6221,10 +6221,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121125734</v>
+        <v>121125733</v>
       </c>
       <c r="B49" t="n">
-        <v>94723</v>
+        <v>5171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6233,25 +6233,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>210</v>
+        <v>102204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693862</v>
+        <v>694003</v>
       </c>
       <c r="R49" t="n">
-        <v>6552120</v>
+        <v>6552176</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6323,10 +6323,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121125733</v>
+        <v>121125734</v>
       </c>
       <c r="B50" t="n">
-        <v>5171</v>
+        <v>94723</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6335,25 +6335,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102204</v>
+        <v>210</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>694003</v>
+        <v>693862</v>
       </c>
       <c r="R50" t="n">
-        <v>6552176</v>
+        <v>6552120</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -6221,10 +6221,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121125733</v>
+        <v>121125734</v>
       </c>
       <c r="B49" t="n">
-        <v>5171</v>
+        <v>94728</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6233,25 +6233,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102204</v>
+        <v>210</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>694003</v>
+        <v>693862</v>
       </c>
       <c r="R49" t="n">
-        <v>6552176</v>
+        <v>6552120</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6323,10 +6323,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121125734</v>
+        <v>121125733</v>
       </c>
       <c r="B50" t="n">
-        <v>94723</v>
+        <v>5172</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6335,25 +6335,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>210</v>
+        <v>102204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6363,10 +6363,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>693862</v>
+        <v>694003</v>
       </c>
       <c r="R50" t="n">
-        <v>6552120</v>
+        <v>6552176</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6428,7 +6428,7 @@
         <v>121108561</v>
       </c>
       <c r="B51" t="n">
-        <v>8424</v>
+        <v>8425</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>121342637</v>
       </c>
       <c r="B52" t="n">
-        <v>94627</v>
+        <v>94635</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -6657,7 +6657,7 @@
         <v>126838536</v>
       </c>
       <c r="B53" t="n">
-        <v>95714</v>
+        <v>95789</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>126838533</v>
       </c>
       <c r="B54" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>126838537</v>
       </c>
       <c r="B55" t="n">
-        <v>90805</v>
+        <v>90879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>126838535</v>
       </c>
       <c r="B57" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -6657,7 +6657,7 @@
         <v>126838536</v>
       </c>
       <c r="B53" t="n">
-        <v>95789</v>
+        <v>95795</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>126838533</v>
       </c>
       <c r="B54" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>126838537</v>
       </c>
       <c r="B55" t="n">
-        <v>90879</v>
+        <v>90885</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>126838535</v>
       </c>
       <c r="B57" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -6657,7 +6657,7 @@
         <v>126838536</v>
       </c>
       <c r="B53" t="n">
-        <v>95795</v>
+        <v>95796</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>126838537</v>
       </c>
       <c r="B55" t="n">
-        <v>90885</v>
+        <v>90886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>126838535</v>
       </c>
       <c r="B57" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -6657,7 +6657,7 @@
         <v>126838536</v>
       </c>
       <c r="B53" t="n">
-        <v>95796</v>
+        <v>95800</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>126838533</v>
       </c>
       <c r="B54" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>126838537</v>
       </c>
       <c r="B55" t="n">
-        <v>90886</v>
+        <v>90890</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>126838539</v>
       </c>
       <c r="B56" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>126838535</v>
       </c>
       <c r="B57" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -6657,7 +6657,7 @@
         <v>126838536</v>
       </c>
       <c r="B53" t="n">
-        <v>95800</v>
+        <v>95789</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>126838533</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>126838537</v>
       </c>
       <c r="B55" t="n">
-        <v>90890</v>
+        <v>90879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>126838539</v>
       </c>
       <c r="B56" t="n">
-        <v>57658</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>126838535</v>
       </c>
       <c r="B57" t="n">
-        <v>91350</v>
+        <v>91339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -4767,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -6657,7 +6657,7 @@
         <v>126838536</v>
       </c>
       <c r="B53" t="n">
-        <v>95789</v>
+        <v>95800</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>126838533</v>
       </c>
       <c r="B54" t="n">
-        <v>79629</v>
+        <v>79636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>126838537</v>
       </c>
       <c r="B55" t="n">
-        <v>90879</v>
+        <v>90890</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>126838539</v>
       </c>
       <c r="B56" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>126838535</v>
       </c>
       <c r="B57" t="n">
-        <v>91339</v>
+        <v>91350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97610588</v>
+        <v>97610374</v>
       </c>
       <c r="B2" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>693837.3265427987</v>
+        <v>693809</v>
       </c>
       <c r="R2" t="n">
-        <v>6551987.622512593</v>
+        <v>6552094</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2021-12-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,51 +774,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97611459</v>
+        <v>97610588</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694080.5320007298</v>
+        <v>693837</v>
       </c>
       <c r="R3" t="n">
-        <v>6552208.58094582</v>
+        <v>6551988</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,19 +844,9 @@
           <t>2021-12-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97611579</v>
+        <v>97610935</v>
       </c>
       <c r="B4" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>694094.9378939504</v>
+        <v>693947</v>
       </c>
       <c r="R4" t="n">
-        <v>6552178.92011114</v>
+        <v>6552093</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,19 +943,9 @@
           <t>2021-12-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97610374</v>
+        <v>99519442</v>
       </c>
       <c r="B5" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,21 +1001,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693809.2631913492</v>
+        <v>694057</v>
       </c>
       <c r="R5" t="n">
-        <v>6552093.347955291</v>
+        <v>6552225</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,22 +1037,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,66 +1062,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97610629</v>
+        <v>121125734</v>
       </c>
       <c r="B6" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>693837.3265427987</v>
+        <v>693862</v>
       </c>
       <c r="R6" t="n">
-        <v>6551987.622512593</v>
+        <v>6552120</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,22 +1139,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,67 +1159,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97609813</v>
+        <v>126838537</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>936</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spinnfingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lentaria byssiseda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Haninge, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>693876.9640157013</v>
+        <v>693871</v>
       </c>
       <c r="R7" t="n">
-        <v>6552244.101827199</v>
+        <v>6552130</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1236,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,64 +1256,58 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97610520</v>
+        <v>97610629</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>693799.7674930182</v>
+        <v>693837</v>
       </c>
       <c r="R8" t="n">
-        <v>6552046.505354621</v>
+        <v>6551988</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,19 +1337,9 @@
           <t>2021-12-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,52 +1366,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97610935</v>
+        <v>97611199</v>
       </c>
       <c r="B9" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>693947.0582614073</v>
+        <v>693995</v>
       </c>
       <c r="R9" t="n">
-        <v>6552093.12046787</v>
+        <v>6552173</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,19 +1435,9 @@
           <t>2021-12-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,19 +1464,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97611199</v>
+        <v>97611459</v>
       </c>
       <c r="B10" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1626,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>693995.0841376819</v>
+        <v>694081</v>
       </c>
       <c r="R10" t="n">
-        <v>6552173.854426938</v>
+        <v>6552209</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1659,19 +1533,9 @@
           <t>2021-12-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-12-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,47 +1562,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99509589</v>
+        <v>99509403</v>
       </c>
       <c r="B11" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1444</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1748,13 +1602,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>693816.4495974419</v>
+        <v>693812</v>
       </c>
       <c r="R11" t="n">
-        <v>6552216.309810633</v>
+        <v>6552151</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,7 +1637,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1647,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,15 +1674,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99508526</v>
+        <v>97611579</v>
       </c>
       <c r="B12" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,21 +1685,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1858,17 +1707,17 @@
       <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>693812.5315312629</v>
+        <v>694095</v>
       </c>
       <c r="R12" t="n">
-        <v>6552049.212583828</v>
+        <v>6552179</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,22 +1741,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,27 +1761,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99519442</v>
+        <v>99519456</v>
       </c>
       <c r="B13" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1950,21 +1784,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1974,10 +1808,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>694057.4872960745</v>
+        <v>694035</v>
       </c>
       <c r="R13" t="n">
-        <v>6552225.440632967</v>
+        <v>6552166</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2007,24 +1841,9 @@
           <t>2022-03-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,53 +1870,52 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99519427</v>
+        <v>112170183</v>
       </c>
       <c r="B14" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>694039.1733442071</v>
+        <v>693999</v>
       </c>
       <c r="R14" t="n">
-        <v>6552169.394265341</v>
+        <v>6552112</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2121,27 +1939,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Flera stora kuddar i blåbärsris.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,33 +1968,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99519456</v>
+        <v>112170184</v>
       </c>
       <c r="B15" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,17 +2023,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>694035.2120400621</v>
+        <v>693995</v>
       </c>
       <c r="R15" t="n">
-        <v>6552166.102602915</v>
+        <v>6552132</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2238,22 +2057,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2264,31 +2083,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99509403</v>
+        <v>112170187</v>
       </c>
       <c r="B16" t="n">
-        <v>81961</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,42 +2115,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1444</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>693811.5206198564</v>
+        <v>694042</v>
       </c>
       <c r="R16" t="n">
-        <v>6552150.640746157</v>
+        <v>6552162</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2355,22 +2173,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stor kudde.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,33 +2202,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99509808</v>
+        <v>112170191</v>
       </c>
       <c r="B17" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,48 +2232,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219711</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>693824.4645471055</v>
+        <v>694068</v>
       </c>
       <c r="R17" t="n">
-        <v>6552241.441077345</v>
+        <v>6552282</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,22 +2290,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Stor kudde.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,33 +2319,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Fuktig granskog med tall och björk.</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99509809</v>
+        <v>121108157</v>
       </c>
       <c r="B18" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,39 +2354,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Badkobben, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>693824.4645471055</v>
+        <v>693874</v>
       </c>
       <c r="R18" t="n">
-        <v>6552241.441077345</v>
+        <v>6552257</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2592,22 +2416,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2622,65 +2446,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99519425</v>
+        <v>112170180</v>
       </c>
       <c r="B19" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>2590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>694037.2253306459</v>
+        <v>693927</v>
       </c>
       <c r="R19" t="n">
-        <v>6552156.932589144</v>
+        <v>6552111</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2704,22 +2523,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,69 +2549,69 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten klen låga i sumpskog.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99519428</v>
+        <v>112170177</v>
       </c>
       <c r="B20" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>694088.181875264</v>
+        <v>693885</v>
       </c>
       <c r="R20" t="n">
-        <v>6552159.517886163</v>
+        <v>6552077</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2816,27 +2635,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2847,79 +2661,69 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Vid basen av klippvägg.</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>99508876</v>
+        <v>112170178</v>
       </c>
       <c r="B21" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>693709.1211158735</v>
+        <v>693918</v>
       </c>
       <c r="R21" t="n">
-        <v>6552093.941633398</v>
+        <v>6552119</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2943,22 +2747,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2023-09-17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,49 +2777,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>99519421</v>
+        <v>121125725</v>
       </c>
       <c r="B22" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>2818</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3025,13 +2824,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>694062.6159321242</v>
+        <v>693735</v>
       </c>
       <c r="R22" t="n">
-        <v>6552134.525110744</v>
+        <v>6552057</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3055,22 +2854,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,71 +2868,71 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>99519422</v>
+        <v>121342637</v>
       </c>
       <c r="B23" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>694050.425397313</v>
+        <v>693881</v>
       </c>
       <c r="R23" t="n">
-        <v>6552161.208071223</v>
+        <v>6552133</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3167,22 +2956,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,33 +2970,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>99508962</v>
+        <v>126838536</v>
       </c>
       <c r="B24" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3225,46 +3000,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>693714.829385159</v>
+        <v>693874</v>
       </c>
       <c r="R24" t="n">
-        <v>6552103.50291712</v>
+        <v>6552135</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3288,22 +3054,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3312,34 +3068,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99508936</v>
+        <v>121110360</v>
       </c>
       <c r="B25" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,44 +3097,44 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>5420</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>693714.829385159</v>
+        <v>693858</v>
       </c>
       <c r="R25" t="n">
-        <v>6552103.50291712</v>
+        <v>6551956</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3408,22 +3158,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växte vid gammal tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,65 +3193,61 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristina Bäck</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111541130</v>
+        <v>97609962</v>
       </c>
       <c r="B26" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Okänt, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>693830.8333423812</v>
+        <v>693781</v>
       </c>
       <c r="R26" t="n">
-        <v>6552176.860022029</v>
+        <v>6552195</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3520,22 +3271,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3546,11 +3287,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3560,60 +3296,56 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111541116</v>
+        <v>97611505</v>
       </c>
       <c r="B27" t="n">
-        <v>108219</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Haninge, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>693830.7552326696</v>
+        <v>694138</v>
       </c>
       <c r="R27" t="n">
-        <v>6552178.401404973</v>
+        <v>6552181</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3637,22 +3369,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3663,11 +3385,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3677,60 +3394,65 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111541117</v>
+        <v>99508876</v>
       </c>
       <c r="B28" t="n">
-        <v>108219</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219711</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ornö, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>693809.5100469354</v>
+        <v>693709</v>
       </c>
       <c r="R28" t="n">
-        <v>6552200.504896822</v>
+        <v>6552094</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3754,22 +3476,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3780,74 +3502,74 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, Karolin Hård</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112170177</v>
+        <v>99509589</v>
       </c>
       <c r="B29" t="n">
-        <v>93357</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2667</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>693885</v>
+        <v>693816</v>
       </c>
       <c r="R29" t="n">
-        <v>6552076</v>
+        <v>6552216</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3871,22 +3593,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3897,36 +3619,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Vid basen av klippvägg.</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112170186</v>
+        <v>99519425</v>
       </c>
       <c r="B30" t="n">
-        <v>78281</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3934,37 +3646,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>694041</v>
+        <v>694037</v>
       </c>
       <c r="R30" t="n">
         <v>6552157</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3988,22 +3700,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:37</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4014,56 +3716,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Gammal torr tallåga</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal torr tallåga</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112170151</v>
+        <v>112170185</v>
       </c>
       <c r="B31" t="n">
-        <v>56477</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4071,21 +3743,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4095,13 +3767,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>693854</v>
+        <v>694000</v>
       </c>
       <c r="R31" t="n">
-        <v>6552210</v>
+        <v>6552145</v>
       </c>
       <c r="S31" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4130,7 +3802,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4140,12 +3812,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Läte nere vid vattnet.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4156,6 +3823,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Gammal levande tall</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Gammal levande tall</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4172,57 +3864,55 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112170191</v>
+        <v>121121931</v>
       </c>
       <c r="B32" t="n">
-        <v>93592</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Ornö Bodal, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>694067</v>
+        <v>693888</v>
       </c>
       <c r="R32" t="n">
-        <v>6552283</v>
+        <v>6552263</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4246,27 +3936,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Stor kudde.</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4279,70 +3954,60 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Fuktig granskog med tall och björk.</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Gabriella Westberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Gabriella Westberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112170178</v>
+        <v>126838535</v>
       </c>
       <c r="B33" t="n">
-        <v>93373</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693919</v>
+        <v>693784</v>
       </c>
       <c r="R33" t="n">
-        <v>6552120</v>
+        <v>6552183</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4369,22 +4034,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4399,70 +4054,67 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112170182</v>
+        <v>121109702</v>
       </c>
       <c r="B34" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106554</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693976</v>
+        <v>693904</v>
       </c>
       <c r="R34" t="n">
-        <v>6552129</v>
+        <v>6551983</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4486,22 +4138,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Växte vid tallhällmark</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4510,95 +4167,67 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Björklåga med det mesta av barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Betula # Björklåga med det mesta av barken kvar.</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112170187</v>
+        <v>99519421</v>
       </c>
       <c r="B35" t="n">
-        <v>93592</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>694042</v>
+        <v>694062</v>
       </c>
       <c r="R35" t="n">
-        <v>6552162</v>
+        <v>6552134</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4622,27 +4251,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Stor kudde.</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4651,77 +4265,66 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112170190</v>
+        <v>99519422</v>
       </c>
       <c r="B36" t="n">
-        <v>5123</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>694070</v>
+        <v>694050</v>
       </c>
       <c r="R36" t="n">
-        <v>6552221</v>
+        <v>6552161</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4745,119 +4348,80 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112170183</v>
+        <v>99519423</v>
       </c>
       <c r="B37" t="n">
-        <v>93592</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>693999</v>
+        <v>693955</v>
       </c>
       <c r="R37" t="n">
-        <v>6552113</v>
+        <v>6552075</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4881,27 +4445,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Flera stora kuddar i blåbärsris.</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4910,61 +4459,50 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112170180</v>
+        <v>112170186</v>
       </c>
       <c r="B38" t="n">
-        <v>94379</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2590</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4974,10 +4512,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693927</v>
+        <v>694041</v>
       </c>
       <c r="R38" t="n">
-        <v>6552111</v>
+        <v>6552157</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5009,7 +4547,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5019,7 +4557,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5031,9 +4569,29 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Gammal torr tallåga</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten klen låga i sumpskog.</t>
+          <t>Pinus sylvestris # Gammal torr tallåga</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5051,15 +4609,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112170185</v>
+        <v>121228311</v>
       </c>
       <c r="B39" t="n">
-        <v>89612</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5067,37 +4620,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>694000</v>
+        <v>693786</v>
       </c>
       <c r="R39" t="n">
-        <v>6552145</v>
+        <v>6552132</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5121,22 +4677,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5145,93 +4691,64 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Gammal levande tall</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Gammal levande tall</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Roja Kirkeby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112170184</v>
+        <v>126838533</v>
       </c>
       <c r="B40" t="n">
-        <v>93592</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>693996</v>
+        <v>693781</v>
       </c>
       <c r="R40" t="n">
-        <v>6552132</v>
+        <v>6552153</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5258,22 +4775,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5284,36 +4791,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112170188</v>
+        <v>99519427</v>
       </c>
       <c r="B41" t="n">
-        <v>4727</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5321,54 +4818,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gråberget, Ornö, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>694095</v>
+        <v>694039</v>
       </c>
       <c r="R41" t="n">
-        <v>6552131</v>
+        <v>6552169</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5392,22 +4872,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:06</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-09-17</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:06</t>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5416,54 +4891,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Äldre grovbarkig levande gran.</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies # Äldre grovbarkig levande gran.</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121108431</v>
+        <v>99519428</v>
       </c>
       <c r="B42" t="n">
-        <v>100364</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5471,41 +4920,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Badkobben, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>693829</v>
+        <v>694088</v>
       </c>
       <c r="R42" t="n">
-        <v>6552190</v>
+        <v>6552160</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5529,22 +4974,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:13</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:13</t>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5559,27 +4999,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121108157</v>
+        <v>126838539</v>
       </c>
       <c r="B43" t="n">
-        <v>94870</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5587,45 +5022,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Badkobben, Srm</t>
+          <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693874</v>
+        <v>693919</v>
       </c>
       <c r="R43" t="n">
-        <v>6552257</v>
+        <v>6552192</v>
       </c>
       <c r="S43" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5649,22 +5076,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5679,27 +5096,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121108905</v>
+        <v>99508962</v>
       </c>
       <c r="B44" t="n">
-        <v>8435</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5707,42 +5119,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Badkobben, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>693732</v>
+        <v>693715</v>
       </c>
       <c r="R44" t="n">
-        <v>6552059</v>
+        <v>6552104</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5766,22 +5182,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5790,33 +5206,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121125725</v>
+        <v>112170190</v>
       </c>
       <c r="B45" t="n">
-        <v>94620</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5824,37 +5236,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>693735</v>
+        <v>694070</v>
       </c>
       <c r="R45" t="n">
-        <v>6552057</v>
+        <v>6552222</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5878,48 +5295,72 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121125724</v>
+        <v>101667199</v>
       </c>
       <c r="B46" t="n">
-        <v>5192</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57754</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5927,37 +5368,57 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>102118</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Gråberget, Ornö, Mörbyfjärden, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693779</v>
+        <v>694028</v>
       </c>
       <c r="R46" t="n">
-        <v>6552034</v>
+        <v>6552131</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5981,12 +5442,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>06:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Sågs flyga upp från marken, satte sig en kort stund i ett träd ca. 20 m bort.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6001,49 +5477,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Per Flodby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121125740</v>
+        <v>121125733</v>
       </c>
       <c r="B47" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5178</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106554</v>
+        <v>102204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6053,10 +5524,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>693742</v>
+        <v>694003</v>
       </c>
       <c r="R47" t="n">
-        <v>6552063</v>
+        <v>6552176</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -6115,56 +5586,65 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121228311</v>
+        <v>112170188</v>
       </c>
       <c r="B48" t="n">
-        <v>79227</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>102306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>693786</v>
+        <v>694096</v>
       </c>
       <c r="R48" t="n">
-        <v>6552132</v>
+        <v>6552131</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6188,12 +5668,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6206,30 +5696,45 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # Äldre grovbarkig levande gran.</t>
+        </is>
+      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121125734</v>
+        <v>100529723</v>
       </c>
       <c r="B49" t="n">
-        <v>94728</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6237,37 +5742,52 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>210</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Bodal, Ornö, Haninge, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693862</v>
+        <v>693812</v>
       </c>
       <c r="R49" t="n">
-        <v>6552120</v>
+        <v>6552160</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6291,12 +5811,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6311,49 +5831,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Tiina Laantee</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Tiina Laantee</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121125733</v>
+        <v>121125724</v>
       </c>
       <c r="B50" t="n">
-        <v>5172</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102204</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6363,10 +5878,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>694003</v>
+        <v>693779</v>
       </c>
       <c r="R50" t="n">
-        <v>6552176</v>
+        <v>6552034</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6425,15 +5940,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121108561</v>
+        <v>99508936</v>
       </c>
       <c r="B51" t="n">
-        <v>8425</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6441,46 +5951,44 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Badkobben, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>693800</v>
+        <v>693715</v>
       </c>
       <c r="R51" t="n">
-        <v>6552126</v>
+        <v>6552104</v>
       </c>
       <c r="S51" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6504,22 +6012,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6528,34 +6036,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Kristina Bäck</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121342637</v>
+        <v>121108905</v>
       </c>
       <c r="B52" t="n">
-        <v>94635</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6563,41 +6065,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2818</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Badkobben, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>693881</v>
+        <v>693732</v>
       </c>
       <c r="R52" t="n">
-        <v>6552133</v>
+        <v>6552059</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6621,12 +6124,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6635,29 +6148,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roja Kirkeby</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126838536</v>
+        <v>112170182</v>
       </c>
       <c r="B53" t="n">
-        <v>95800</v>
+        <v>8444</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6665,34 +6177,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2818</v>
+        <v>106554</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Gråberget, Ornö, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693874</v>
+        <v>693975</v>
       </c>
       <c r="R53" t="n">
-        <v>6552135</v>
+        <v>6552128</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6719,12 +6236,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2023-09-17</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6735,64 +6262,93 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Björklåga med det mesta av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Betula # Björklåga med det mesta av barken kvar.</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Klas Magnusson, Måns Persson, Per Flodby</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126838533</v>
+        <v>121108561</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>8444</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>106554</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gråberget, Srm</t>
+          <t>Badkobben, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693781</v>
+        <v>693800</v>
       </c>
       <c r="R54" t="n">
-        <v>6552153</v>
+        <v>6552126</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6816,12 +6372,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6830,66 +6396,76 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126838537</v>
+        <v>121109626</v>
       </c>
       <c r="B55" t="n">
-        <v>90890</v>
+        <v>8444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>936</v>
+        <v>106554</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spinnfingersvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lentaria byssiseda</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Corner</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gråberget, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693871</v>
+        <v>693894</v>
       </c>
       <c r="R55" t="n">
-        <v>6552130</v>
+        <v>6552013</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6913,12 +6489,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6933,44 +6519,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126838539</v>
+        <v>121125740</v>
       </c>
       <c r="B56" t="n">
-        <v>57658</v>
+        <v>8444</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6980,13 +6566,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>693919</v>
+        <v>693742</v>
       </c>
       <c r="R56" t="n">
-        <v>6552192</v>
+        <v>6552063</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7010,12 +6596,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7030,44 +6616,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126838535</v>
+        <v>126838546</v>
       </c>
       <c r="B57" t="n">
-        <v>91350</v>
+        <v>8444</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>106554</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7077,10 +6663,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693784</v>
+        <v>693769</v>
       </c>
       <c r="R57" t="n">
-        <v>6552183</v>
+        <v>6552187</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7136,6 +6722,1178 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>99509808</v>
+      </c>
+      <c r="B58" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gråberget, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>693824</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6552241</v>
+      </c>
+      <c r="S58" t="n">
+        <v>8</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>111541116</v>
+      </c>
+      <c r="B59" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>693831</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6552179</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Karolin Hård</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>111541117</v>
+      </c>
+      <c r="B60" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>693810</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6552200</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Karolin Hård</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>97627108</v>
+      </c>
+      <c r="B61" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2m Ö om stig, Srm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>693895</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6552098</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>99508526</v>
+      </c>
+      <c r="B62" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Gråberget, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>693813</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6552049</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>97609813</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Haninge, Srm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>693877</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6552245</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>97610520</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Haninge, Srm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>693800</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6552046</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2021-12-18</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>99509809</v>
+      </c>
+      <c r="B65" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gråberget, Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>693824</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6552241</v>
+      </c>
+      <c r="S65" t="n">
+        <v>8</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2022-03-28</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>111541130</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ornö, Srm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>693831</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6552177</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, Karolin Hård</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>121108431</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Badkobben, Srm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>693829</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6552190</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>121227976</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Badkobben, Srm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>693857</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6552175</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Ornö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Blad</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Roja Kirkeby</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 67868-2021 artfynd.xlsx
+++ b/artfynd/A 67868-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97610374</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97610588</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97610935</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519442</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,6 +1193,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125734</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1265,6 +1295,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838537</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97610629</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97611199</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97611459</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99509403</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1770,6 +1825,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97611579</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1867,6 +1927,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519456</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170183</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170184</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170187</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2340,6 +2420,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170191</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2455,6 +2540,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121108157</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2567,6 +2657,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170180</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2679,6 +2774,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170177</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2786,6 +2886,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170178</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2884,6 +2989,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125725</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2986,6 +3096,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121342637</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3083,6 +3198,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838536</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3202,6 +3322,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121110360</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3300,6 +3425,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97609962</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3398,6 +3528,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97611505</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3515,6 +3650,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99508876</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3632,6 +3772,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99509589</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3729,6 +3874,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519425</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3861,6 +4011,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170185</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3966,6 +4121,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121121931</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4063,6 +4223,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838535</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4183,6 +4348,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121109702</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4280,6 +4450,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519421</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4377,6 +4552,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519422</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4474,6 +4654,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519423</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4606,6 +4791,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170186</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4707,6 +4897,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121228311</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4804,6 +4999,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838533</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4906,6 +5106,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519427</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5008,6 +5213,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519428</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5105,6 +5315,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838539</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5222,6 +5437,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99508962</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5354,6 +5574,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170190</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5486,6 +5711,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101667199</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5583,6 +5813,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125733</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5728,6 +5963,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170188</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5840,6 +6080,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100529723</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5937,6 +6182,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125724</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6051,6 +6301,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99508936</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6163,6 +6418,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121108905</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6295,6 +6555,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112170182</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6412,6 +6677,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121108561</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6528,6 +6798,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121109626</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6625,6 +6900,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125740</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6722,6 +7002,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838546</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6840,6 +7125,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99509808</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6942,6 +7232,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541116</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7044,6 +7339,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541117</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7158,6 +7458,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97627108</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7267,6 +7572,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99508526</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7366,6 +7676,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97609813</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7465,6 +7780,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97610520</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7574,6 +7894,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99509809</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7676,6 +8001,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111541130</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7787,6 +8117,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121108431</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7894,8 +8229,82 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227976</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>